--- a/downloads/statistical_analysis_results.xlsx
+++ b/downloads/statistical_analysis_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xingqian/Desktop/replicate_pack/downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{997CD23C-14BC-A54A-95ED-CC2E5B28F2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC142E6-68BA-954E-B10F-A5474A2D7B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9840" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{B9E509F4-26C7-1842-BB4C-9030A2E3792B}"/>
+    <workbookView xWindow="6520" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{B9E509F4-26C7-1842-BB4C-9030A2E3792B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>model</t>
   </si>
@@ -57,12 +57,6 @@
   </si>
   <si>
     <t>Cliff’s delta</t>
-  </si>
-  <si>
-    <t>single llm mean</t>
-  </si>
-  <si>
-    <t>multi agent mean</t>
   </si>
 </sst>
 </file>
@@ -459,97 +453,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50834DF8-EC40-2846-B7D1-9C5B0F8EF4CD}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="23.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>0.63329999999999997</v>
-      </c>
-      <c r="C2">
-        <v>0.8</v>
-      </c>
-      <c r="D2" s="2">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0.16669999999999999</v>
+      <c r="B2" s="2">
+        <v>0.13477900000000001</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.09</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>0.7</v>
-      </c>
-      <c r="C3">
-        <v>0.75</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.54359999999999997</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.05</v>
+      <c r="B3" s="2">
+        <v>0.20429700000000001</v>
+      </c>
+      <c r="C3" s="2">
+        <v>-0.08</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>0.88329999999999997</v>
-      </c>
-      <c r="C4">
-        <v>0.9667</v>
-      </c>
-      <c r="D4" s="2">
-        <v>8.5400000000000004E-2</v>
-      </c>
-      <c r="E4" s="2">
-        <v>8.3299999999999999E-2</v>
+      <c r="B4" s="2">
+        <v>4.8453999999999997E-2</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>0.63329999999999997</v>
-      </c>
-      <c r="C5">
-        <v>0.95</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="B5" s="2">
         <v>0</v>
       </c>
-      <c r="E5" s="2">
-        <v>0.31669999999999998</v>
+      <c r="C5" s="2">
+        <v>0.28000000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/statistical_analysis_results.xlsx
+++ b/downloads/statistical_analysis_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xingqian/Desktop/replicate_pack/downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC142E6-68BA-954E-B10F-A5474A2D7B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{997CD23C-14BC-A54A-95ED-CC2E5B28F2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6520" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{B9E509F4-26C7-1842-BB4C-9030A2E3792B}"/>
+    <workbookView xWindow="9840" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{B9E509F4-26C7-1842-BB4C-9030A2E3792B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>model</t>
   </si>
@@ -57,6 +57,12 @@
   </si>
   <si>
     <t>Cliff’s delta</t>
+  </si>
+  <si>
+    <t>single llm mean</t>
+  </si>
+  <si>
+    <t>multi agent mean</t>
   </si>
 </sst>
 </file>
@@ -453,65 +459,97 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50834DF8-EC40-2846-B7D1-9C5B0F8EF4CD}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="23.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
-        <v>0.13477900000000001</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0.09</v>
+      <c r="B2">
+        <v>0.63329999999999997</v>
+      </c>
+      <c r="C2">
+        <v>0.8</v>
+      </c>
+      <c r="D2" s="2">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.16669999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
-        <v>0.20429700000000001</v>
-      </c>
-      <c r="C3" s="2">
-        <v>-0.08</v>
+      <c r="B3">
+        <v>0.7</v>
+      </c>
+      <c r="C3">
+        <v>0.75</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.54359999999999997</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
-        <v>4.8453999999999997E-2</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.1</v>
+      <c r="B4">
+        <v>0.88329999999999997</v>
+      </c>
+      <c r="C4">
+        <v>0.9667</v>
+      </c>
+      <c r="D4" s="2">
+        <v>8.5400000000000004E-2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
+        <v>0.63329999999999997</v>
+      </c>
+      <c r="C5">
+        <v>0.95</v>
+      </c>
+      <c r="D5" s="2">
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <v>0.28000000000000003</v>
+      <c r="E5" s="2">
+        <v>0.31669999999999998</v>
       </c>
     </row>
   </sheetData>
